--- a/app/static/storage/MRC Preparation 2026.xlsx
+++ b/app/static/storage/MRC Preparation 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Supreme Court\Desktop\Clerk II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6C00EE-FD1C-4DD2-8739-ED29D6A10BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62901443-4968-426C-92AA-40338F94BEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{90D5A3ED-4359-4A84-9398-0CE82921C746}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{90D5A3ED-4359-4A84-9398-0CE82921C746}"/>
   </bookViews>
   <sheets>
     <sheet name="2026_-_Criminal" sheetId="1" r:id="rId1"/>
@@ -1997,7 +1997,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2042,12 +2042,6 @@
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
@@ -2075,14 +2069,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2106,9 +2094,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2123,9 +2108,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2236,15 +2218,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2254,15 +2230,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2279,9 +2246,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2309,9 +2273,83 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Heading" xfId="1" xr:uid="{26C2C80A-D561-435F-99C1-E45637C4F5F3}"/>
@@ -2341,7 +2379,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1347962</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>263402</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="356" cy="356"/>
@@ -2384,7 +2422,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1347962</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>263402</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="356" cy="356"/>
@@ -2427,7 +2465,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1347962</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>263402</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="356" cy="356"/>
@@ -2470,7 +2508,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1347962</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>263402</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="356" cy="356"/>
@@ -2847,2981 +2885,2976 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="50" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="2" spans="2:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="57">
+      <c r="B2" s="51">
         <v>1</v>
       </c>
-      <c r="C2" s="57">
+      <c r="C2" s="51">
         <v>4734</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="60">
+      <c r="F2" s="54">
         <v>46029</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="56" t="s">
+      <c r="G2" s="55"/>
+      <c r="H2" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="3" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="57">
+      <c r="B3" s="51">
         <v>2</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="51">
         <v>4735</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="54">
         <v>46029</v>
       </c>
-      <c r="G3" s="61"/>
-      <c r="H3" s="56" t="s">
+      <c r="G3" s="55"/>
+      <c r="H3" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="4" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="57">
+      <c r="B4" s="51">
         <v>3</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="51">
         <v>4736</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="54">
         <v>46034</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="56" t="s">
+      <c r="G4" s="55"/>
+      <c r="H4" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="57">
+      <c r="B5" s="51">
         <v>4</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="51">
         <v>4737</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="60">
+      <c r="F5" s="54">
         <v>46034</v>
       </c>
-      <c r="G5" s="61"/>
-      <c r="H5" s="56" t="s">
+      <c r="G5" s="55"/>
+      <c r="H5" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="57">
+      <c r="B6" s="51">
         <v>5</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="51">
         <v>4738</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="60">
+      <c r="F6" s="54">
         <v>46036</v>
       </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="7" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="57">
+      <c r="B7" s="51">
         <v>6</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="51">
         <v>4739</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="54">
         <v>46036</v>
       </c>
-      <c r="G7" s="61"/>
-      <c r="H7" s="56" t="s">
+      <c r="G7" s="55"/>
+      <c r="H7" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="8" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="57">
+      <c r="B8" s="51">
         <v>7</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="51">
         <v>4740</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="61"/>
-      <c r="H8" s="56" t="s">
+      <c r="G8" s="55"/>
+      <c r="H8" s="50" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="57">
+    <row r="9" spans="2:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="51">
         <v>1</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="51">
         <v>4732</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="54">
         <v>46037</v>
       </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61" t="s">
+      <c r="G9" s="55"/>
+      <c r="H9" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="57">
+    <row r="10" spans="2:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="51">
         <v>2</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="51">
         <v>4733</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="54">
         <v>46037</v>
       </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61" t="s">
+      <c r="G10" s="55"/>
+      <c r="H10" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="57">
+    <row r="11" spans="2:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="51">
         <v>3</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="51">
         <v>4734</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="57" t="s">
+      <c r="E11" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="54">
         <v>46037</v>
       </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61" t="s">
+      <c r="G11" s="55"/>
+      <c r="H11" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="12" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="57">
+    <row r="12" spans="2:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="51">
         <v>4</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="51">
         <v>4735</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="54">
         <v>46037</v>
       </c>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61" t="s">
+      <c r="G12" s="55"/>
+      <c r="H12" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="57">
+    <row r="13" spans="2:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B13" s="51">
         <v>5</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="51">
         <v>4736</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="54">
         <v>46037</v>
       </c>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61" t="s">
+      <c r="G13" s="55"/>
+      <c r="H13" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="14" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="57">
+    <row r="14" spans="2:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B14" s="51">
         <v>6</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="51">
         <v>4738</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="54">
         <v>46037</v>
       </c>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61" t="s">
+      <c r="G14" s="55"/>
+      <c r="H14" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="57">
+    <row r="15" spans="2:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="51">
         <v>7</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="51">
         <v>4739</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="54">
         <v>46037</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61" t="s">
+      <c r="G15" s="55"/>
+      <c r="H15" s="55" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="57">
+    <row r="16" spans="2:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="51">
         <v>8</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="51">
         <v>4737</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="54">
         <v>46051</v>
       </c>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61" t="s">
+      <c r="G16" s="55"/>
+      <c r="H16" s="55" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="17" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="57">
+      <c r="B17" s="51">
         <v>1</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="51">
         <v>4568</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="D17" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="61" t="s">
+      <c r="H17" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="18" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="57">
+      <c r="B18" s="51">
         <v>2</v>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="51">
         <v>4648</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="60">
+      <c r="F18" s="54">
         <v>45819</v>
       </c>
-      <c r="G18" s="107" t="s">
+      <c r="G18" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="61" t="s">
+      <c r="H18" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="19" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="57">
+      <c r="B19" s="51">
         <v>3</v>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="51">
         <v>4671</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="60">
+      <c r="F19" s="54">
         <v>45866</v>
       </c>
-      <c r="G19" s="107" t="s">
+      <c r="G19" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="61" t="s">
+      <c r="H19" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="20" spans="2:8" customFormat="1" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="57">
+      <c r="B20" s="51">
         <v>4</v>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="51">
         <v>4674</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="107" t="s">
+      <c r="G20" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="61" t="s">
+      <c r="H20" s="55" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="2:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B21" s="57">
+    <row r="21" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="51">
         <v>5</v>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="51">
         <v>4693</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="60">
+      <c r="F21" s="54">
         <v>45919</v>
       </c>
-      <c r="G21" s="106" t="s">
+      <c r="G21" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="H21" s="61" t="s">
+      <c r="H21" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="22" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="57">
+      <c r="B22" s="51">
         <v>6</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="51">
         <v>4715</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="D22" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="60">
+      <c r="F22" s="54">
         <v>45979</v>
       </c>
-      <c r="G22" s="106" t="s">
+      <c r="G22" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H22" s="61" t="s">
+      <c r="H22" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="23" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="57">
+      <c r="B23" s="51">
         <v>7</v>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="51">
         <v>4716</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="D23" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F23" s="54">
         <v>45979</v>
       </c>
-      <c r="G23" s="106" t="s">
+      <c r="G23" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="61" t="s">
+      <c r="H23" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="24" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="57">
+      <c r="B24" s="51">
         <v>8</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="51">
         <v>4717</v>
       </c>
-      <c r="D24" s="72" t="s">
+      <c r="D24" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="72" t="s">
+      <c r="E24" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="60">
+      <c r="F24" s="54">
         <v>45979</v>
       </c>
-      <c r="G24" s="106" t="s">
+      <c r="G24" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="61" t="s">
+      <c r="H24" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="25" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="57">
+      <c r="B25" s="51">
         <v>9</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="51">
         <v>4718</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="72" t="s">
+      <c r="E25" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="60">
+      <c r="F25" s="54">
         <v>45979</v>
       </c>
-      <c r="G25" s="106" t="s">
+      <c r="G25" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H25" s="61" t="s">
+      <c r="H25" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="26" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="57">
+      <c r="B26" s="51">
         <v>10</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="51">
         <v>4719</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D26" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="72" t="s">
+      <c r="E26" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="60">
+      <c r="F26" s="54">
         <v>45979</v>
       </c>
-      <c r="G26" s="106" t="s">
+      <c r="G26" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="61" t="s">
+      <c r="H26" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="27" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="57">
+      <c r="B27" s="51">
         <v>11</v>
       </c>
-      <c r="C27" s="57">
+      <c r="C27" s="51">
         <v>4720</v>
       </c>
-      <c r="D27" s="72" t="s">
+      <c r="D27" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="72" t="s">
+      <c r="E27" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="60">
+      <c r="F27" s="54">
         <v>45979</v>
       </c>
-      <c r="G27" s="106" t="s">
+      <c r="G27" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H27" s="61" t="s">
+      <c r="H27" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="28" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="57">
+      <c r="B28" s="51">
         <v>12</v>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="51">
         <v>4721</v>
       </c>
-      <c r="D28" s="72" t="s">
+      <c r="D28" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="72" t="s">
+      <c r="E28" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="60">
+      <c r="F28" s="54">
         <v>45979</v>
       </c>
-      <c r="G28" s="106" t="s">
+      <c r="G28" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="61" t="s">
+      <c r="H28" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="29" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="57">
+      <c r="B29" s="51">
         <v>13</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="51">
         <v>4722</v>
       </c>
-      <c r="D29" s="72" t="s">
+      <c r="D29" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="60">
+      <c r="F29" s="54">
         <v>45979</v>
       </c>
-      <c r="G29" s="106" t="s">
+      <c r="G29" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H29" s="61" t="s">
+      <c r="H29" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="30" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="57">
+      <c r="B30" s="51">
         <v>14</v>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="51">
         <v>4723</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="72" t="s">
+      <c r="E30" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="60">
+      <c r="F30" s="54">
         <v>45979</v>
       </c>
-      <c r="G30" s="106" t="s">
+      <c r="G30" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H30" s="61" t="s">
+      <c r="H30" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="57">
+      <c r="B31" s="51">
         <v>15</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C31" s="51">
         <v>4724</v>
       </c>
-      <c r="D31" s="72" t="s">
+      <c r="D31" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="72" t="s">
+      <c r="E31" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="60">
+      <c r="F31" s="54">
         <v>45979</v>
       </c>
-      <c r="G31" s="106" t="s">
+      <c r="G31" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="61" t="s">
+      <c r="H31" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="32" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="57">
+      <c r="B32" s="51">
         <v>16</v>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="51">
         <v>4725</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D32" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="72" t="s">
+      <c r="E32" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="60">
+      <c r="F32" s="54">
         <v>45979</v>
       </c>
-      <c r="G32" s="106" t="s">
+      <c r="G32" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="61" t="s">
+      <c r="H32" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="33" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="57">
+      <c r="B33" s="51">
         <v>17</v>
       </c>
-      <c r="C33" s="57">
+      <c r="C33" s="51">
         <v>4726</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D33" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="72" t="s">
+      <c r="E33" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="60">
+      <c r="F33" s="54">
         <v>45979</v>
       </c>
-      <c r="G33" s="106" t="s">
+      <c r="G33" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="61" t="s">
+      <c r="H33" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="34" spans="2:8" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="57">
+      <c r="B34" s="51">
         <v>18</v>
       </c>
-      <c r="C34" s="57">
+      <c r="C34" s="51">
         <v>4740</v>
       </c>
-      <c r="D34" s="72" t="s">
+      <c r="D34" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="73" t="s">
+      <c r="E34" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="107" t="s">
+      <c r="G34" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="H34" s="61" t="s">
+      <c r="H34" s="55" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="35" spans="2:8" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="57">
+      <c r="B35" s="51">
         <v>1</v>
       </c>
-      <c r="C35" s="108">
+      <c r="C35" s="96">
         <v>4741</v>
       </c>
-      <c r="D35" s="58" t="s">
+      <c r="D35" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="E35" s="73" t="s">
+      <c r="E35" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="60">
+      <c r="F35" s="54">
         <v>46059</v>
       </c>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61" t="s">
+      <c r="G35" s="55"/>
+      <c r="H35" s="55" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="36" spans="2:8" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="57">
+      <c r="B36" s="51">
         <v>2</v>
       </c>
-      <c r="C36" s="57">
+      <c r="C36" s="51">
         <v>4742</v>
       </c>
-      <c r="D36" s="58" t="s">
+      <c r="D36" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="E36" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="60">
+      <c r="F36" s="54">
         <v>46072</v>
       </c>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61" t="s">
+      <c r="G36" s="55"/>
+      <c r="H36" s="55" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="37" spans="2:8" customFormat="1" ht="114.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="71">
+    <row r="37" spans="2:8" customFormat="1" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="65">
         <v>1</v>
       </c>
-      <c r="C37" s="57">
+      <c r="C37" s="51">
         <v>4568</v>
       </c>
-      <c r="D37" s="72" t="s">
+      <c r="D37" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="58" t="s">
+      <c r="E37" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="73" t="s">
+      <c r="F37" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61" t="s">
+      <c r="G37" s="55"/>
+      <c r="H37" s="55" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="2:8" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="71">
+    <row r="38" spans="2:8" customFormat="1" ht="43.5" x14ac:dyDescent="0.25">
+      <c r="B38" s="65">
         <v>2</v>
       </c>
-      <c r="C38" s="57">
+      <c r="C38" s="51">
         <v>4648</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="D38" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="72" t="s">
+      <c r="E38" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="74" t="s">
+      <c r="F38" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61" t="s">
+      <c r="G38" s="55"/>
+      <c r="H38" s="55" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="39" spans="2:8" customFormat="1" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="71">
+    <row r="39" spans="2:8" customFormat="1" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="65">
         <v>3</v>
       </c>
-      <c r="C39" s="57">
+      <c r="C39" s="51">
         <v>4740</v>
       </c>
-      <c r="D39" s="72" t="s">
+      <c r="D39" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="74" t="s">
+      <c r="F39" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61" t="s">
+      <c r="G39" s="55"/>
+      <c r="H39" s="55" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="40" spans="2:8" customFormat="1" ht="86.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="71">
+    <row r="40" spans="2:8" customFormat="1" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="B40" s="65">
         <v>4</v>
       </c>
-      <c r="C40" s="108">
+      <c r="C40" s="96">
         <v>4741</v>
       </c>
-      <c r="D40" s="58" t="s">
+      <c r="D40" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="74" t="s">
+      <c r="F40" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61" t="s">
+      <c r="G40" s="55"/>
+      <c r="H40" s="55" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="41" spans="2:8" customFormat="1" ht="86.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="71">
+    <row r="41" spans="2:8" customFormat="1" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="65">
         <v>5</v>
       </c>
-      <c r="C41" s="57">
+      <c r="C41" s="51">
         <v>4742</v>
       </c>
-      <c r="D41" s="58" t="s">
+      <c r="D41" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="74" t="s">
+      <c r="F41" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61" t="s">
+      <c r="G41" s="55"/>
+      <c r="H41" s="55" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="42" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="57">
+      <c r="B42" s="51">
         <v>1</v>
       </c>
-      <c r="C42" s="57">
+      <c r="C42" s="51">
         <v>4671</v>
       </c>
-      <c r="D42" s="72" t="s">
+      <c r="D42" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="72" t="s">
+      <c r="E42" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="60">
+      <c r="F42" s="54">
         <v>45866</v>
       </c>
-      <c r="G42" s="107" t="s">
+      <c r="G42" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="H42" s="61" t="s">
+      <c r="H42" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="43" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="57">
+      <c r="B43" s="51">
         <v>2</v>
       </c>
-      <c r="C43" s="57">
+      <c r="C43" s="51">
         <v>4674</v>
       </c>
-      <c r="D43" s="72" t="s">
+      <c r="D43" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="78" t="s">
+      <c r="E43" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F43" s="73" t="s">
+      <c r="F43" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G43" s="107" t="s">
+      <c r="G43" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="H43" s="61" t="s">
+      <c r="H43" s="55" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="44" spans="2:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B44" s="57">
+    <row r="44" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="51">
         <v>3</v>
       </c>
-      <c r="C44" s="57">
+      <c r="C44" s="51">
         <v>4693</v>
       </c>
-      <c r="D44" s="72" t="s">
+      <c r="D44" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E44" s="58" t="s">
+      <c r="E44" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="F44" s="60">
+      <c r="F44" s="54">
         <v>45919</v>
       </c>
-      <c r="G44" s="106" t="s">
+      <c r="G44" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="H44" s="61" t="s">
+      <c r="H44" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="45" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="57">
+      <c r="B45" s="51">
         <v>4</v>
       </c>
-      <c r="C45" s="57">
+      <c r="C45" s="51">
         <v>4715</v>
       </c>
-      <c r="D45" s="72" t="s">
+      <c r="D45" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="58" t="s">
+      <c r="E45" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="60">
+      <c r="F45" s="54">
         <v>45979</v>
       </c>
-      <c r="G45" s="106" t="s">
+      <c r="G45" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H45" s="61" t="s">
+      <c r="H45" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="46" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="57">
+      <c r="B46" s="51">
         <v>5</v>
       </c>
-      <c r="C46" s="57">
+      <c r="C46" s="51">
         <v>4716</v>
       </c>
-      <c r="D46" s="72" t="s">
+      <c r="D46" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E46" s="58" t="s">
+      <c r="E46" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="60">
+      <c r="F46" s="54">
         <v>45979</v>
       </c>
-      <c r="G46" s="106" t="s">
+      <c r="G46" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H46" s="61" t="s">
+      <c r="H46" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="47" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="57">
+      <c r="B47" s="51">
         <v>6</v>
       </c>
-      <c r="C47" s="57">
+      <c r="C47" s="51">
         <v>4717</v>
       </c>
-      <c r="D47" s="72" t="s">
+      <c r="D47" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E47" s="72" t="s">
+      <c r="E47" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="60">
+      <c r="F47" s="54">
         <v>45979</v>
       </c>
-      <c r="G47" s="106" t="s">
+      <c r="G47" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H47" s="61" t="s">
+      <c r="H47" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="48" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="57">
+      <c r="B48" s="51">
         <v>7</v>
       </c>
-      <c r="C48" s="57">
+      <c r="C48" s="51">
         <v>4718</v>
       </c>
-      <c r="D48" s="72" t="s">
+      <c r="D48" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E48" s="72" t="s">
+      <c r="E48" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F48" s="60">
+      <c r="F48" s="54">
         <v>45979</v>
       </c>
-      <c r="G48" s="106" t="s">
+      <c r="G48" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="61" t="s">
+      <c r="H48" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="49" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="57">
+      <c r="B49" s="51">
         <v>8</v>
       </c>
-      <c r="C49" s="57">
+      <c r="C49" s="51">
         <v>4719</v>
       </c>
-      <c r="D49" s="72" t="s">
+      <c r="D49" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="72" t="s">
+      <c r="E49" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="60">
+      <c r="F49" s="54">
         <v>45979</v>
       </c>
-      <c r="G49" s="106" t="s">
+      <c r="G49" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H49" s="61" t="s">
+      <c r="H49" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="50" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="57">
+      <c r="B50" s="51">
         <v>9</v>
       </c>
-      <c r="C50" s="57">
+      <c r="C50" s="51">
         <v>4720</v>
       </c>
-      <c r="D50" s="72" t="s">
+      <c r="D50" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="60">
+      <c r="F50" s="54">
         <v>45979</v>
       </c>
-      <c r="G50" s="106" t="s">
+      <c r="G50" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H50" s="61" t="s">
+      <c r="H50" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="51" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="57">
+      <c r="B51" s="51">
         <v>10</v>
       </c>
-      <c r="C51" s="57">
+      <c r="C51" s="51">
         <v>4721</v>
       </c>
-      <c r="D51" s="72" t="s">
+      <c r="D51" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E51" s="72" t="s">
+      <c r="E51" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F51" s="60">
+      <c r="F51" s="54">
         <v>45979</v>
       </c>
-      <c r="G51" s="106" t="s">
+      <c r="G51" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H51" s="61" t="s">
+      <c r="H51" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="52" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="57">
+      <c r="B52" s="51">
         <v>11</v>
       </c>
-      <c r="C52" s="57">
+      <c r="C52" s="51">
         <v>4722</v>
       </c>
-      <c r="D52" s="72" t="s">
+      <c r="D52" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E52" s="72" t="s">
+      <c r="E52" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F52" s="60">
+      <c r="F52" s="54">
         <v>45979</v>
       </c>
-      <c r="G52" s="106" t="s">
+      <c r="G52" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="61" t="s">
+      <c r="H52" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="53" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="57">
+      <c r="B53" s="51">
         <v>12</v>
       </c>
-      <c r="C53" s="57">
+      <c r="C53" s="51">
         <v>4723</v>
       </c>
-      <c r="D53" s="72" t="s">
+      <c r="D53" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E53" s="72" t="s">
+      <c r="E53" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="60">
+      <c r="F53" s="54">
         <v>45979</v>
       </c>
-      <c r="G53" s="106" t="s">
+      <c r="G53" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="61" t="s">
+      <c r="H53" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="54" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="57">
+      <c r="B54" s="51">
         <v>13</v>
       </c>
-      <c r="C54" s="57">
+      <c r="C54" s="51">
         <v>4724</v>
       </c>
-      <c r="D54" s="72" t="s">
+      <c r="D54" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E54" s="72" t="s">
+      <c r="E54" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="60">
+      <c r="F54" s="54">
         <v>45979</v>
       </c>
-      <c r="G54" s="106" t="s">
+      <c r="G54" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="61" t="s">
+      <c r="H54" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="55" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="57">
+      <c r="B55" s="51">
         <v>14</v>
       </c>
-      <c r="C55" s="57">
+      <c r="C55" s="51">
         <v>4725</v>
       </c>
-      <c r="D55" s="72" t="s">
+      <c r="D55" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E55" s="72" t="s">
+      <c r="E55" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F55" s="60">
+      <c r="F55" s="54">
         <v>45979</v>
       </c>
-      <c r="G55" s="106" t="s">
+      <c r="G55" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="61" t="s">
+      <c r="H55" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="56" spans="2:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="57">
+      <c r="B56" s="51">
         <v>15</v>
       </c>
-      <c r="C56" s="57">
+      <c r="C56" s="51">
         <v>4726</v>
       </c>
-      <c r="D56" s="72" t="s">
+      <c r="D56" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E56" s="72" t="s">
+      <c r="E56" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="54">
         <v>45979</v>
       </c>
-      <c r="G56" s="106" t="s">
+      <c r="G56" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="61" t="s">
+      <c r="H56" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="57">
+      <c r="B57" s="51">
         <v>16</v>
       </c>
-      <c r="C57" s="57">
+      <c r="C57" s="51">
         <v>4713</v>
       </c>
-      <c r="D57" s="56" t="s">
+      <c r="D57" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E57" s="56" t="s">
+      <c r="E57" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="F57" s="109" t="s">
+      <c r="F57" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="G57" s="56" t="s">
+      <c r="G57" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="H57" s="61" t="s">
+      <c r="H57" s="55" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="99.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="57">
+      <c r="B58" s="51">
         <v>1</v>
       </c>
-      <c r="C58" s="108" t="s">
+      <c r="C58" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="D58" s="58" t="s">
+      <c r="D58" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="73" t="s">
+      <c r="E58" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="60">
+      <c r="F58" s="54">
         <v>46084</v>
       </c>
-      <c r="G58" s="61"/>
-      <c r="H58" s="56" t="s">
+      <c r="G58" s="55"/>
+      <c r="H58" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="57">
+      <c r="B59" s="51">
         <v>2</v>
       </c>
-      <c r="C59" s="57">
+      <c r="C59" s="51">
         <v>4744</v>
       </c>
-      <c r="D59" s="58" t="s">
+      <c r="D59" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E59" s="73" t="s">
+      <c r="E59" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="F59" s="60">
+      <c r="F59" s="54">
         <v>46090</v>
       </c>
-      <c r="G59" s="61"/>
-      <c r="H59" s="56" t="s">
+      <c r="G59" s="55"/>
+      <c r="H59" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="60" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="57">
+      <c r="B60" s="51">
         <v>3</v>
       </c>
-      <c r="C60" s="57">
+      <c r="C60" s="51">
         <v>4745</v>
       </c>
-      <c r="D60" s="58" t="s">
+      <c r="D60" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="73" t="s">
+      <c r="E60" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="F60" s="60">
+      <c r="F60" s="54">
         <v>46090</v>
       </c>
-      <c r="G60" s="61"/>
-      <c r="H60" s="56" t="s">
+      <c r="G60" s="55"/>
+      <c r="H60" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="61" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="57">
+      <c r="B61" s="51">
         <v>4</v>
       </c>
-      <c r="C61" s="57">
+      <c r="C61" s="51">
         <v>4746</v>
       </c>
-      <c r="D61" s="58" t="s">
+      <c r="D61" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="E61" s="73" t="s">
+      <c r="E61" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="60">
+      <c r="F61" s="54">
         <v>46106</v>
       </c>
-      <c r="G61" s="61"/>
-      <c r="H61" s="56" t="s">
+      <c r="G61" s="55"/>
+      <c r="H61" s="50" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="100.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="71">
+    <row r="62" spans="2:8" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="65">
         <v>1</v>
       </c>
-      <c r="C62" s="108" t="s">
+      <c r="C62" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="D62" s="58" t="s">
+      <c r="D62" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="73" t="s">
+      <c r="E62" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="F62" s="74" t="s">
+      <c r="F62" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="G62" s="61"/>
-      <c r="H62" s="56" t="s">
+      <c r="G62" s="55"/>
+      <c r="H62" s="50" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="71">
+    <row r="63" spans="2:8" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="65">
         <v>2</v>
       </c>
-      <c r="C63" s="57">
+      <c r="C63" s="51">
         <v>4744</v>
       </c>
-      <c r="D63" s="58" t="s">
+      <c r="D63" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E63" s="73" t="s">
+      <c r="E63" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="F63" s="74" t="s">
+      <c r="F63" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="G63" s="61"/>
-      <c r="H63" s="56" t="s">
+      <c r="G63" s="55"/>
+      <c r="H63" s="50" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="71">
+    <row r="64" spans="2:8" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="65">
         <v>3</v>
       </c>
-      <c r="C64" s="57">
+      <c r="C64" s="51">
         <v>4745</v>
       </c>
-      <c r="D64" s="58" t="s">
+      <c r="D64" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="73" t="s">
+      <c r="E64" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="F64" s="73" t="s">
+      <c r="F64" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="G64" s="61"/>
-      <c r="H64" s="56" t="s">
+      <c r="G64" s="55"/>
+      <c r="H64" s="50" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="57">
+      <c r="B65" s="51">
         <v>1</v>
       </c>
-      <c r="C65" s="57">
+      <c r="C65" s="51">
         <v>4671</v>
       </c>
-      <c r="D65" s="72" t="s">
+      <c r="D65" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="72" t="s">
+      <c r="E65" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="60">
+      <c r="F65" s="54">
         <v>45866</v>
       </c>
-      <c r="G65" s="107" t="s">
+      <c r="G65" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="H65" s="56" t="s">
+      <c r="H65" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="57">
+      <c r="B66" s="51">
         <v>2</v>
       </c>
-      <c r="C66" s="57">
+      <c r="C66" s="51">
         <v>4674</v>
       </c>
-      <c r="D66" s="72" t="s">
+      <c r="D66" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="E66" s="78" t="s">
+      <c r="E66" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="73" t="s">
+      <c r="F66" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G66" s="107" t="s">
+      <c r="G66" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="H66" s="56" t="s">
+      <c r="H66" s="50" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B67" s="57">
+    <row r="67" spans="2:8" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="51">
         <v>3</v>
       </c>
-      <c r="C67" s="57">
+      <c r="C67" s="51">
         <v>4693</v>
       </c>
-      <c r="D67" s="72" t="s">
+      <c r="D67" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E67" s="58" t="s">
+      <c r="E67" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="F67" s="60">
+      <c r="F67" s="54">
         <v>45919</v>
       </c>
-      <c r="G67" s="106" t="s">
+      <c r="G67" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="H67" s="56" t="s">
+      <c r="H67" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="57">
+      <c r="B68" s="51">
         <v>4</v>
       </c>
-      <c r="C68" s="57">
+      <c r="C68" s="51">
         <v>4715</v>
       </c>
-      <c r="D68" s="72" t="s">
+      <c r="D68" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E68" s="58" t="s">
+      <c r="E68" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="60">
+      <c r="F68" s="54">
         <v>45979</v>
       </c>
-      <c r="G68" s="107" t="s">
+      <c r="G68" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H68" s="56" t="s">
+      <c r="H68" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="57">
+      <c r="B69" s="51">
         <v>5</v>
       </c>
-      <c r="C69" s="57">
+      <c r="C69" s="51">
         <v>4716</v>
       </c>
-      <c r="D69" s="72" t="s">
+      <c r="D69" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E69" s="58" t="s">
+      <c r="E69" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="60">
+      <c r="F69" s="54">
         <v>45979</v>
       </c>
-      <c r="G69" s="107" t="s">
+      <c r="G69" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H69" s="56" t="s">
+      <c r="H69" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="57">
+      <c r="B70" s="51">
         <v>6</v>
       </c>
-      <c r="C70" s="57">
+      <c r="C70" s="51">
         <v>4717</v>
       </c>
-      <c r="D70" s="72" t="s">
+      <c r="D70" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E70" s="72" t="s">
+      <c r="E70" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F70" s="60">
+      <c r="F70" s="54">
         <v>45979</v>
       </c>
-      <c r="G70" s="107" t="s">
+      <c r="G70" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H70" s="56" t="s">
+      <c r="H70" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="57">
+      <c r="B71" s="51">
         <v>7</v>
       </c>
-      <c r="C71" s="57">
+      <c r="C71" s="51">
         <v>4718</v>
       </c>
-      <c r="D71" s="72" t="s">
+      <c r="D71" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E71" s="72" t="s">
+      <c r="E71" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F71" s="60">
+      <c r="F71" s="54">
         <v>45979</v>
       </c>
-      <c r="G71" s="107" t="s">
+      <c r="G71" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H71" s="56" t="s">
+      <c r="H71" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="57">
+      <c r="B72" s="51">
         <v>8</v>
       </c>
-      <c r="C72" s="57">
+      <c r="C72" s="51">
         <v>4719</v>
       </c>
-      <c r="D72" s="72" t="s">
+      <c r="D72" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E72" s="72" t="s">
+      <c r="E72" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="60">
+      <c r="F72" s="54">
         <v>45979</v>
       </c>
-      <c r="G72" s="107" t="s">
+      <c r="G72" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H72" s="56" t="s">
+      <c r="H72" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="57">
+      <c r="B73" s="51">
         <v>9</v>
       </c>
-      <c r="C73" s="57">
+      <c r="C73" s="51">
         <v>4720</v>
       </c>
-      <c r="D73" s="72" t="s">
+      <c r="D73" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E73" s="72" t="s">
+      <c r="E73" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F73" s="60">
+      <c r="F73" s="54">
         <v>45979</v>
       </c>
-      <c r="G73" s="107" t="s">
+      <c r="G73" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H73" s="56" t="s">
+      <c r="H73" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="57">
+      <c r="B74" s="51">
         <v>10</v>
       </c>
-      <c r="C74" s="57">
+      <c r="C74" s="51">
         <v>4721</v>
       </c>
-      <c r="D74" s="72" t="s">
+      <c r="D74" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E74" s="72" t="s">
+      <c r="E74" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F74" s="60">
+      <c r="F74" s="54">
         <v>45979</v>
       </c>
-      <c r="G74" s="107" t="s">
+      <c r="G74" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H74" s="56" t="s">
+      <c r="H74" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="57">
+      <c r="B75" s="51">
         <v>11</v>
       </c>
-      <c r="C75" s="57">
+      <c r="C75" s="51">
         <v>4722</v>
       </c>
-      <c r="D75" s="72" t="s">
+      <c r="D75" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E75" s="72" t="s">
+      <c r="E75" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="60">
+      <c r="F75" s="54">
         <v>45979</v>
       </c>
-      <c r="G75" s="107" t="s">
+      <c r="G75" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H75" s="56" t="s">
+      <c r="H75" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="57">
+      <c r="B76" s="51">
         <v>12</v>
       </c>
-      <c r="C76" s="57">
+      <c r="C76" s="51">
         <v>4723</v>
       </c>
-      <c r="D76" s="72" t="s">
+      <c r="D76" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E76" s="72" t="s">
+      <c r="E76" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="60">
+      <c r="F76" s="54">
         <v>45979</v>
       </c>
-      <c r="G76" s="107" t="s">
+      <c r="G76" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H76" s="56" t="s">
+      <c r="H76" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="57">
+      <c r="B77" s="51">
         <v>13</v>
       </c>
-      <c r="C77" s="57">
+      <c r="C77" s="51">
         <v>4724</v>
       </c>
-      <c r="D77" s="72" t="s">
+      <c r="D77" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E77" s="72" t="s">
+      <c r="E77" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="60">
+      <c r="F77" s="54">
         <v>45979</v>
       </c>
-      <c r="G77" s="107" t="s">
+      <c r="G77" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="56" t="s">
+      <c r="H77" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="57">
+      <c r="B78" s="51">
         <v>14</v>
       </c>
-      <c r="C78" s="57">
+      <c r="C78" s="51">
         <v>4725</v>
       </c>
-      <c r="D78" s="72" t="s">
+      <c r="D78" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E78" s="72" t="s">
+      <c r="E78" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="60">
+      <c r="F78" s="54">
         <v>45979</v>
       </c>
-      <c r="G78" s="107" t="s">
+      <c r="G78" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H78" s="56" t="s">
+      <c r="H78" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="57">
+      <c r="B79" s="51">
         <v>15</v>
       </c>
-      <c r="C79" s="57">
+      <c r="C79" s="51">
         <v>4726</v>
       </c>
-      <c r="D79" s="72" t="s">
+      <c r="D79" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E79" s="72" t="s">
+      <c r="E79" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="60">
+      <c r="F79" s="54">
         <v>45979</v>
       </c>
-      <c r="G79" s="107" t="s">
+      <c r="G79" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="H79" s="56" t="s">
+      <c r="H79" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="57">
+      <c r="B80" s="51">
         <v>16</v>
       </c>
-      <c r="C80" s="57">
+      <c r="C80" s="51">
         <v>4713</v>
       </c>
-      <c r="D80" s="56" t="s">
+      <c r="D80" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E80" s="56" t="s">
+      <c r="E80" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="F80" s="109" t="s">
+      <c r="F80" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="56" t="s">
+      <c r="G80" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="H80" s="56" t="s">
+      <c r="H80" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="30.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="57">
+      <c r="B81" s="51">
         <v>17</v>
       </c>
-      <c r="C81" s="57">
+      <c r="C81" s="51">
         <v>4746</v>
       </c>
-      <c r="D81" s="58" t="s">
+      <c r="D81" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="E81" s="73" t="s">
+      <c r="E81" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="F81" s="60">
+      <c r="F81" s="54">
         <v>46106</v>
       </c>
-      <c r="G81" s="109" t="s">
+      <c r="G81" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="H81" s="56" t="s">
+      <c r="H81" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="57">
+      <c r="B82" s="51">
         <v>1</v>
       </c>
-      <c r="C82" s="108" t="s">
+      <c r="C82" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="D82" s="58" t="s">
+      <c r="D82" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="E82" s="73" t="s">
+      <c r="E82" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="60">
+      <c r="F82" s="54">
         <v>46084</v>
       </c>
-      <c r="G82" s="61"/>
-      <c r="H82" s="56" t="s">
+      <c r="G82" s="55"/>
+      <c r="H82" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="83" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="57">
+      <c r="B83" s="51">
         <v>2</v>
       </c>
-      <c r="C83" s="57">
+      <c r="C83" s="51">
         <v>4748</v>
       </c>
-      <c r="D83" s="58" t="s">
+      <c r="D83" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E83" s="73" t="s">
+      <c r="E83" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="F83" s="60">
+      <c r="F83" s="54">
         <v>46134</v>
       </c>
-      <c r="G83" s="61"/>
-      <c r="H83" s="56" t="s">
+      <c r="G83" s="55"/>
+      <c r="H83" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="57">
+      <c r="B84" s="51">
         <v>3</v>
       </c>
-      <c r="C84" s="57">
+      <c r="C84" s="51">
         <v>4749</v>
       </c>
-      <c r="D84" s="58" t="s">
+      <c r="D84" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E84" s="73" t="s">
+      <c r="E84" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="F84" s="60">
+      <c r="F84" s="54">
         <v>46134</v>
       </c>
-      <c r="G84" s="61"/>
-      <c r="H84" s="56" t="s">
+      <c r="G84" s="55"/>
+      <c r="H84" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="57">
+      <c r="B85" s="51">
         <v>4</v>
       </c>
-      <c r="C85" s="57">
+      <c r="C85" s="51">
         <v>4750</v>
       </c>
-      <c r="D85" s="58" t="s">
+      <c r="D85" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="E85" s="73" t="s">
+      <c r="E85" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="F85" s="60">
+      <c r="F85" s="54">
         <v>46135</v>
       </c>
-      <c r="G85" s="61"/>
-      <c r="H85" s="56" t="s">
+      <c r="G85" s="55"/>
+      <c r="H85" s="50" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="71">
+    <row r="86" spans="2:8" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="65">
         <v>1</v>
       </c>
-      <c r="C86" s="108" t="s">
+      <c r="C86" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="D86" s="58" t="s">
+      <c r="D86" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="E86" s="73" t="s">
+      <c r="E86" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="74" t="s">
+      <c r="F86" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="G86" s="61"/>
-      <c r="H86" s="56" t="s">
+      <c r="G86" s="55"/>
+      <c r="H86" s="50" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="44.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="57">
+      <c r="B87" s="51">
         <v>1</v>
       </c>
-      <c r="C87" s="57">
+      <c r="C87" s="51">
         <v>4671</v>
       </c>
-      <c r="D87" s="72" t="s">
+      <c r="D87" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E87" s="72" t="s">
+      <c r="E87" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F87" s="60">
+      <c r="F87" s="54">
         <v>45866</v>
       </c>
-      <c r="G87" s="107" t="s">
+      <c r="G87" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="H87" s="56" t="s">
+      <c r="H87" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="57">
+      <c r="B88" s="51">
         <v>2</v>
       </c>
-      <c r="C88" s="57">
+      <c r="C88" s="51">
         <v>4674</v>
       </c>
-      <c r="D88" s="72" t="s">
+      <c r="D88" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="E88" s="78" t="s">
+      <c r="E88" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="73" t="s">
+      <c r="F88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G88" s="107" t="s">
+      <c r="G88" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="H88" s="56" t="s">
+      <c r="H88" s="50" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B89" s="57">
+    <row r="89" spans="2:8" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="51">
         <v>3</v>
       </c>
-      <c r="C89" s="57">
+      <c r="C89" s="51">
         <v>4693</v>
       </c>
-      <c r="D89" s="72" t="s">
+      <c r="D89" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E89" s="58" t="s">
+      <c r="E89" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="F89" s="60">
+      <c r="F89" s="54">
         <v>45919</v>
       </c>
-      <c r="G89" s="106" t="s">
+      <c r="G89" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="H89" s="56" t="s">
+      <c r="H89" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="57">
+      <c r="B90" s="51">
         <v>4</v>
       </c>
-      <c r="C90" s="57">
+      <c r="C90" s="51">
         <v>4715</v>
       </c>
-      <c r="D90" s="72" t="s">
+      <c r="D90" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="58" t="s">
+      <c r="E90" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="60">
+      <c r="F90" s="54">
         <v>45979</v>
       </c>
-      <c r="G90" s="107" t="s">
+      <c r="G90" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H90" s="56" t="s">
+      <c r="H90" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="57">
+      <c r="B91" s="51">
         <v>5</v>
       </c>
-      <c r="C91" s="57">
+      <c r="C91" s="51">
         <v>4716</v>
       </c>
-      <c r="D91" s="72" t="s">
+      <c r="D91" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E91" s="58" t="s">
+      <c r="E91" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="60">
+      <c r="F91" s="54">
         <v>45979</v>
       </c>
-      <c r="G91" s="107" t="s">
+      <c r="G91" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H91" s="56" t="s">
+      <c r="H91" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="57">
+      <c r="B92" s="51">
         <v>6</v>
       </c>
-      <c r="C92" s="57">
+      <c r="C92" s="51">
         <v>4717</v>
       </c>
-      <c r="D92" s="72" t="s">
+      <c r="D92" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E92" s="72" t="s">
+      <c r="E92" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="60">
+      <c r="F92" s="54">
         <v>45979</v>
       </c>
-      <c r="G92" s="107" t="s">
+      <c r="G92" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H92" s="56" t="s">
+      <c r="H92" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="57">
+      <c r="B93" s="51">
         <v>7</v>
       </c>
-      <c r="C93" s="57">
+      <c r="C93" s="51">
         <v>4718</v>
       </c>
-      <c r="D93" s="72" t="s">
+      <c r="D93" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E93" s="72" t="s">
+      <c r="E93" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F93" s="60">
+      <c r="F93" s="54">
         <v>45979</v>
       </c>
-      <c r="G93" s="107" t="s">
+      <c r="G93" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H93" s="56" t="s">
+      <c r="H93" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="57">
+      <c r="B94" s="51">
         <v>8</v>
       </c>
-      <c r="C94" s="57">
+      <c r="C94" s="51">
         <v>4719</v>
       </c>
-      <c r="D94" s="72" t="s">
+      <c r="D94" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E94" s="72" t="s">
+      <c r="E94" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F94" s="60">
+      <c r="F94" s="54">
         <v>45979</v>
       </c>
-      <c r="G94" s="107" t="s">
+      <c r="G94" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H94" s="56" t="s">
+      <c r="H94" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="57">
+      <c r="B95" s="51">
         <v>9</v>
       </c>
-      <c r="C95" s="57">
+      <c r="C95" s="51">
         <v>4720</v>
       </c>
-      <c r="D95" s="72" t="s">
+      <c r="D95" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E95" s="72" t="s">
+      <c r="E95" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F95" s="60">
+      <c r="F95" s="54">
         <v>45979</v>
       </c>
-      <c r="G95" s="107" t="s">
+      <c r="G95" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H95" s="56" t="s">
+      <c r="H95" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="96" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="57">
+      <c r="B96" s="51">
         <v>10</v>
       </c>
-      <c r="C96" s="57">
+      <c r="C96" s="51">
         <v>4721</v>
       </c>
-      <c r="D96" s="72" t="s">
+      <c r="D96" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E96" s="72" t="s">
+      <c r="E96" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F96" s="60">
+      <c r="F96" s="54">
         <v>45979</v>
       </c>
-      <c r="G96" s="107" t="s">
+      <c r="G96" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H96" s="56" t="s">
+      <c r="H96" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="57">
+      <c r="B97" s="51">
         <v>11</v>
       </c>
-      <c r="C97" s="57">
+      <c r="C97" s="51">
         <v>4722</v>
       </c>
-      <c r="D97" s="72" t="s">
+      <c r="D97" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="72" t="s">
+      <c r="E97" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F97" s="60">
+      <c r="F97" s="54">
         <v>45979</v>
       </c>
-      <c r="G97" s="107" t="s">
+      <c r="G97" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H97" s="56" t="s">
+      <c r="H97" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="57">
+      <c r="B98" s="51">
         <v>12</v>
       </c>
-      <c r="C98" s="57">
+      <c r="C98" s="51">
         <v>4723</v>
       </c>
-      <c r="D98" s="72" t="s">
+      <c r="D98" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E98" s="72" t="s">
+      <c r="E98" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F98" s="60">
+      <c r="F98" s="54">
         <v>45979</v>
       </c>
-      <c r="G98" s="107" t="s">
+      <c r="G98" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H98" s="56" t="s">
+      <c r="H98" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="57">
+      <c r="B99" s="51">
         <v>13</v>
       </c>
-      <c r="C99" s="57">
+      <c r="C99" s="51">
         <v>4724</v>
       </c>
-      <c r="D99" s="72" t="s">
+      <c r="D99" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E99" s="72" t="s">
+      <c r="E99" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F99" s="60">
+      <c r="F99" s="54">
         <v>45979</v>
       </c>
-      <c r="G99" s="107" t="s">
+      <c r="G99" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H99" s="56" t="s">
+      <c r="H99" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="57">
+      <c r="B100" s="51">
         <v>14</v>
       </c>
-      <c r="C100" s="57">
+      <c r="C100" s="51">
         <v>4725</v>
       </c>
-      <c r="D100" s="72" t="s">
+      <c r="D100" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E100" s="72" t="s">
+      <c r="E100" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F100" s="60">
+      <c r="F100" s="54">
         <v>45979</v>
       </c>
-      <c r="G100" s="107" t="s">
+      <c r="G100" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H100" s="56" t="s">
+      <c r="H100" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="57">
+      <c r="B101" s="51">
         <v>15</v>
       </c>
-      <c r="C101" s="57">
+      <c r="C101" s="51">
         <v>4726</v>
       </c>
-      <c r="D101" s="72" t="s">
+      <c r="D101" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E101" s="72" t="s">
+      <c r="E101" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F101" s="60">
+      <c r="F101" s="54">
         <v>45979</v>
       </c>
-      <c r="G101" s="107" t="s">
+      <c r="G101" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="H101" s="56" t="s">
+      <c r="H101" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="102" spans="2:8" ht="105.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="57">
+      <c r="B102" s="51">
         <v>16</v>
       </c>
-      <c r="C102" s="57">
+      <c r="C102" s="51">
         <v>4713</v>
       </c>
-      <c r="D102" s="56" t="s">
+      <c r="D102" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E102" s="56" t="s">
+      <c r="E102" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="F102" s="109" t="s">
+      <c r="F102" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="G102" s="109" t="s">
+      <c r="G102" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="H102" s="56" t="s">
+      <c r="H102" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="57">
+      <c r="B103" s="51">
         <v>17</v>
       </c>
-      <c r="C103" s="57">
+      <c r="C103" s="51">
         <v>4746</v>
       </c>
-      <c r="D103" s="58" t="s">
+      <c r="D103" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="E103" s="73" t="s">
+      <c r="E103" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="F103" s="60">
+      <c r="F103" s="54">
         <v>46106</v>
       </c>
-      <c r="G103" s="109" t="s">
+      <c r="G103" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="H103" s="56" t="s">
+      <c r="H103" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="57">
+      <c r="B104" s="51">
         <v>18</v>
       </c>
-      <c r="C104" s="57">
+      <c r="C104" s="51">
         <v>4748</v>
       </c>
-      <c r="D104" s="58" t="s">
+      <c r="D104" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E104" s="73" t="s">
+      <c r="E104" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="F104" s="60">
+      <c r="F104" s="54">
         <v>46134</v>
       </c>
-      <c r="G104" s="109" t="s">
+      <c r="G104" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="H104" s="56" t="s">
+      <c r="H104" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="46.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="57">
+      <c r="B105" s="51">
         <v>19</v>
       </c>
-      <c r="C105" s="57">
+      <c r="C105" s="51">
         <v>4749</v>
       </c>
-      <c r="D105" s="58" t="s">
+      <c r="D105" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E105" s="73" t="s">
+      <c r="E105" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="F105" s="60">
+      <c r="F105" s="54">
         <v>46134</v>
       </c>
-      <c r="G105" s="109" t="s">
+      <c r="G105" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="H105" s="56" t="s">
+      <c r="H105" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="46.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="57">
+      <c r="B106" s="51">
         <v>20</v>
       </c>
-      <c r="C106" s="57">
+      <c r="C106" s="51">
         <v>4750</v>
       </c>
-      <c r="D106" s="58" t="s">
+      <c r="D106" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="E106" s="73" t="s">
+      <c r="E106" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="F106" s="60">
+      <c r="F106" s="54">
         <v>46135</v>
       </c>
-      <c r="G106" s="109" t="s">
+      <c r="G106" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="H106" s="56" t="s">
+      <c r="H106" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="107" spans="2:8" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="57">
+      <c r="B107" s="51">
         <v>1</v>
       </c>
-      <c r="C107" s="57">
+      <c r="C107" s="51">
         <v>4751</v>
       </c>
-      <c r="D107" s="58" t="s">
+      <c r="D107" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="E107" s="110" t="s">
+      <c r="E107" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="F107" s="110"/>
-      <c r="G107" s="60" t="s">
+      <c r="F107" s="98"/>
+      <c r="G107" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="H107" s="61" t="s">
+      <c r="H107" s="55" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="108" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="57">
+      <c r="B108" s="51">
         <v>2</v>
       </c>
-      <c r="C108" s="57">
+      <c r="C108" s="51">
         <v>4752</v>
       </c>
-      <c r="D108" s="58" t="s">
+      <c r="D108" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="E108" s="110" t="s">
+      <c r="E108" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="F108" s="110"/>
-      <c r="G108" s="60" t="s">
+      <c r="F108" s="98"/>
+      <c r="G108" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="H108" s="61" t="s">
+      <c r="H108" s="55" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="109" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="57">
+      <c r="B109" s="51">
         <v>3</v>
       </c>
-      <c r="C109" s="57">
+      <c r="C109" s="51">
         <v>4753</v>
       </c>
-      <c r="D109" s="58" t="s">
+      <c r="D109" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="E109" s="110" t="s">
+      <c r="E109" s="98" t="s">
         <v>210</v>
       </c>
-      <c r="F109" s="110"/>
-      <c r="G109" s="60" t="s">
+      <c r="F109" s="98"/>
+      <c r="G109" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="H109" s="61" t="s">
+      <c r="H109" s="55" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="2:8" customFormat="1" ht="135" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="62">
+    <row r="110" spans="2:8" customFormat="1" ht="135" x14ac:dyDescent="0.2">
+      <c r="B110" s="56">
         <v>2</v>
       </c>
-      <c r="C110" s="63">
+      <c r="C110" s="57">
         <v>4713</v>
       </c>
-      <c r="D110" s="67" t="s">
+      <c r="D110" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="E110" s="68" t="s">
+      <c r="E110" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="F110" s="69" t="s">
+      <c r="F110" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="G110" s="70" t="s">
+      <c r="G110" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="H110" s="61" t="s">
+      <c r="H110" s="55" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="111" spans="2:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="62">
+    <row r="111" spans="2:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B111" s="56">
         <v>3</v>
       </c>
-      <c r="C111" s="63">
+      <c r="C111" s="57">
         <v>4751</v>
       </c>
-      <c r="D111" s="64" t="s">
+      <c r="D111" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="E111" s="59" t="s">
+      <c r="E111" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="F111" s="65" t="s">
+      <c r="F111" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="G111" s="66" t="s">
+      <c r="G111" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="H111" s="61" t="s">
+      <c r="H111" s="55" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="112" spans="2:8" customFormat="1" ht="44.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="63">
+      <c r="B112" s="57">
         <v>1</v>
       </c>
-      <c r="C112" s="63">
+      <c r="C112" s="57">
         <v>4671</v>
       </c>
-      <c r="D112" s="75" t="s">
+      <c r="D112" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="E112" s="75" t="s">
+      <c r="E112" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F112" s="76">
+      <c r="F112" s="70">
         <v>45866</v>
       </c>
-      <c r="G112" s="77" t="s">
+      <c r="G112" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="H112" s="61" t="s">
+      <c r="H112" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="113" spans="2:8" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="63">
+      <c r="B113" s="57">
         <v>2</v>
       </c>
-      <c r="C113" s="63">
+      <c r="C113" s="57">
         <v>4674</v>
       </c>
-      <c r="D113" s="75" t="s">
+      <c r="D113" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="E113" s="78" t="s">
+      <c r="E113" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F113" s="59" t="s">
+      <c r="F113" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="G113" s="77" t="s">
+      <c r="G113" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="H113" s="61" t="s">
+      <c r="H113" s="55" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="114" spans="2:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B114" s="63">
+    <row r="114" spans="2:8" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="57">
         <v>3</v>
       </c>
-      <c r="C114" s="63">
+      <c r="C114" s="57">
         <v>4693</v>
       </c>
-      <c r="D114" s="75" t="s">
+      <c r="D114" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="E114" s="64" t="s">
+      <c r="E114" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F114" s="76">
+      <c r="F114" s="70">
         <v>45919</v>
       </c>
-      <c r="G114" s="79" t="s">
+      <c r="G114" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="H114" s="61" t="s">
+      <c r="H114" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="115" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="63">
+      <c r="B115" s="57">
         <v>4</v>
       </c>
-      <c r="C115" s="63">
+      <c r="C115" s="57">
         <v>4715</v>
       </c>
-      <c r="D115" s="75" t="s">
+      <c r="D115" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E115" s="64" t="s">
+      <c r="E115" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="F115" s="76">
+      <c r="F115" s="70">
         <v>45979</v>
       </c>
-      <c r="G115" s="77" t="s">
+      <c r="G115" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H115" s="61" t="s">
+      <c r="H115" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="116" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="63">
+      <c r="B116" s="57">
         <v>5</v>
       </c>
-      <c r="C116" s="63">
+      <c r="C116" s="57">
         <v>4716</v>
       </c>
-      <c r="D116" s="75" t="s">
+      <c r="D116" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E116" s="64" t="s">
+      <c r="E116" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="F116" s="76">
+      <c r="F116" s="70">
         <v>45979</v>
       </c>
-      <c r="G116" s="77" t="s">
+      <c r="G116" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H116" s="61" t="s">
+      <c r="H116" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="117" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="63">
+      <c r="B117" s="57">
         <v>6</v>
       </c>
-      <c r="C117" s="63">
+      <c r="C117" s="57">
         <v>4717</v>
       </c>
-      <c r="D117" s="75" t="s">
+      <c r="D117" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E117" s="75" t="s">
+      <c r="E117" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F117" s="76">
+      <c r="F117" s="70">
         <v>45979</v>
       </c>
-      <c r="G117" s="77" t="s">
+      <c r="G117" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H117" s="61" t="s">
+      <c r="H117" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="118" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="63">
+      <c r="B118" s="57">
         <v>7</v>
       </c>
-      <c r="C118" s="63">
+      <c r="C118" s="57">
         <v>4718</v>
       </c>
-      <c r="D118" s="75" t="s">
+      <c r="D118" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E118" s="75" t="s">
+      <c r="E118" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F118" s="76">
+      <c r="F118" s="70">
         <v>45979</v>
       </c>
-      <c r="G118" s="77" t="s">
+      <c r="G118" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H118" s="61" t="s">
+      <c r="H118" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="119" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="63">
+      <c r="B119" s="57">
         <v>8</v>
       </c>
-      <c r="C119" s="63">
+      <c r="C119" s="57">
         <v>4719</v>
       </c>
-      <c r="D119" s="75" t="s">
+      <c r="D119" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E119" s="75" t="s">
+      <c r="E119" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F119" s="76">
+      <c r="F119" s="70">
         <v>45979</v>
       </c>
-      <c r="G119" s="77" t="s">
+      <c r="G119" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H119" s="61" t="s">
+      <c r="H119" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="120" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="63">
+      <c r="B120" s="57">
         <v>9</v>
       </c>
-      <c r="C120" s="63">
+      <c r="C120" s="57">
         <v>4720</v>
       </c>
-      <c r="D120" s="75" t="s">
+      <c r="D120" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E120" s="75" t="s">
+      <c r="E120" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F120" s="76">
+      <c r="F120" s="70">
         <v>45979</v>
       </c>
-      <c r="G120" s="77" t="s">
+      <c r="G120" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H120" s="61" t="s">
+      <c r="H120" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="121" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="63">
+      <c r="B121" s="57">
         <v>10</v>
       </c>
-      <c r="C121" s="63">
+      <c r="C121" s="57">
         <v>4721</v>
       </c>
-      <c r="D121" s="75" t="s">
+      <c r="D121" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E121" s="75" t="s">
+      <c r="E121" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F121" s="76">
+      <c r="F121" s="70">
         <v>45979</v>
       </c>
-      <c r="G121" s="77" t="s">
+      <c r="G121" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H121" s="61" t="s">
+      <c r="H121" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="122" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="63">
+      <c r="B122" s="57">
         <v>11</v>
       </c>
-      <c r="C122" s="63">
+      <c r="C122" s="57">
         <v>4722</v>
       </c>
-      <c r="D122" s="75" t="s">
+      <c r="D122" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E122" s="75" t="s">
+      <c r="E122" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F122" s="76">
+      <c r="F122" s="70">
         <v>45979</v>
       </c>
-      <c r="G122" s="77" t="s">
+      <c r="G122" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H122" s="61" t="s">
+      <c r="H122" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="123" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="63">
+      <c r="B123" s="57">
         <v>12</v>
       </c>
-      <c r="C123" s="63">
+      <c r="C123" s="57">
         <v>4723</v>
       </c>
-      <c r="D123" s="75" t="s">
+      <c r="D123" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E123" s="75" t="s">
+      <c r="E123" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F123" s="76">
+      <c r="F123" s="70">
         <v>45979</v>
       </c>
-      <c r="G123" s="77" t="s">
+      <c r="G123" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H123" s="61" t="s">
+      <c r="H123" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="124" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="63">
+      <c r="B124" s="57">
         <v>13</v>
       </c>
-      <c r="C124" s="63">
+      <c r="C124" s="57">
         <v>4724</v>
       </c>
-      <c r="D124" s="75" t="s">
+      <c r="D124" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E124" s="75" t="s">
+      <c r="E124" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F124" s="76">
+      <c r="F124" s="70">
         <v>45979</v>
       </c>
-      <c r="G124" s="77" t="s">
+      <c r="G124" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H124" s="61" t="s">
+      <c r="H124" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="125" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="63">
+      <c r="B125" s="57">
         <v>14</v>
       </c>
-      <c r="C125" s="63">
+      <c r="C125" s="57">
         <v>4725</v>
       </c>
-      <c r="D125" s="75" t="s">
+      <c r="D125" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E125" s="75" t="s">
+      <c r="E125" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F125" s="76">
+      <c r="F125" s="70">
         <v>45979</v>
       </c>
-      <c r="G125" s="77" t="s">
+      <c r="G125" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H125" s="61" t="s">
+      <c r="H125" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="126" spans="2:8" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="63">
+      <c r="B126" s="57">
         <v>15</v>
       </c>
-      <c r="C126" s="63">
+      <c r="C126" s="57">
         <v>4726</v>
       </c>
-      <c r="D126" s="75" t="s">
+      <c r="D126" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E126" s="75" t="s">
+      <c r="E126" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F126" s="76">
+      <c r="F126" s="70">
         <v>45979</v>
       </c>
-      <c r="G126" s="77" t="s">
+      <c r="G126" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="H126" s="61" t="s">
+      <c r="H126" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="127" spans="2:8" customFormat="1" ht="30.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="63">
+      <c r="B127" s="57">
         <v>16</v>
       </c>
-      <c r="C127" s="63">
+      <c r="C127" s="57">
         <v>4746</v>
       </c>
-      <c r="D127" s="64" t="s">
+      <c r="D127" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="E127" s="59" t="s">
+      <c r="E127" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="F127" s="76">
+      <c r="F127" s="70">
         <v>46106</v>
       </c>
-      <c r="G127" s="69" t="s">
+      <c r="G127" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="H127" s="61" t="s">
+      <c r="H127" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="128" spans="2:8" customFormat="1" ht="31.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="63">
+      <c r="B128" s="57">
         <v>17</v>
       </c>
-      <c r="C128" s="63">
+      <c r="C128" s="57">
         <v>4749</v>
       </c>
-      <c r="D128" s="64" t="s">
+      <c r="D128" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="E128" s="59" t="s">
+      <c r="E128" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="F128" s="76">
+      <c r="F128" s="70">
         <v>46134</v>
       </c>
-      <c r="G128" s="69" t="s">
+      <c r="G128" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="H128" s="61" t="s">
+      <c r="H128" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="129" spans="2:8" customFormat="1" ht="31.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="63">
+      <c r="B129" s="57">
         <v>18</v>
       </c>
-      <c r="C129" s="63">
+      <c r="C129" s="57">
         <v>4750</v>
       </c>
-      <c r="D129" s="64" t="s">
+      <c r="D129" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="E129" s="59" t="s">
+      <c r="E129" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="F129" s="76">
+      <c r="F129" s="70">
         <v>46135</v>
       </c>
-      <c r="G129" s="69" t="s">
+      <c r="G129" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="H129" s="61" t="s">
+      <c r="H129" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="130" spans="2:8" customFormat="1" ht="31.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="63">
+      <c r="B130" s="57">
         <v>19</v>
       </c>
-      <c r="C130" s="63">
+      <c r="C130" s="57">
         <v>4752</v>
       </c>
-      <c r="D130" s="64" t="s">
+      <c r="D130" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="E130" s="59" t="s">
+      <c r="E130" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="F130" s="76" t="s">
+      <c r="F130" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="G130" s="69" t="s">
+      <c r="G130" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="H130" s="61" t="s">
+      <c r="H130" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="131" spans="2:8" customFormat="1" ht="46.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="63">
+      <c r="B131" s="57">
         <v>20</v>
       </c>
-      <c r="C131" s="63">
+      <c r="C131" s="57">
         <v>4753</v>
       </c>
-      <c r="D131" s="64" t="s">
+      <c r="D131" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E131" s="59" t="s">
+      <c r="E131" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="F131" s="76" t="s">
+      <c r="F131" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="G131" s="69" t="s">
+      <c r="G131" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="H131" s="61" t="s">
+      <c r="H131" s="55" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="132" spans="2:8" customFormat="1" ht="226.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="67">
+      <c r="B132" s="61">
         <v>21</v>
       </c>
-      <c r="C132" s="63">
+      <c r="C132" s="57">
         <v>4737</v>
       </c>
-      <c r="D132" s="64" t="s">
+      <c r="D132" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E132" s="59" t="s">
+      <c r="E132" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="F132" s="65" t="s">
+      <c r="F132" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="G132" s="69" t="s">
+      <c r="G132" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="H132" s="61" t="s">
+      <c r="H132" s="55" t="s">
         <v>228</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:H132" xr:uid="{C8B84CDD-DF72-408E-A59C-AAD3EBCC11E1}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="4693"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="p1"/>
-        <filter val="p2"/>
-        <filter val="p3"/>
-        <filter val="p4"/>
-        <filter val="p5"/>
+        <filter val="d1"/>
+        <filter val="d2"/>
+        <filter val="d3"/>
+        <filter val="d4"/>
+        <filter val="d5"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5849,36 +5882,36 @@
   <dimension ref="A1:H79"/>
   <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.21875" style="33" customWidth="1"/>
-    <col min="2" max="2" width="3.88671875" style="33" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" style="33" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="33" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" style="33" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="33" customWidth="1"/>
-    <col min="8" max="16384" width="8.33203125" style="33"/>
+    <col min="1" max="1" width="4.21875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="3.88671875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="29" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="29" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="29" customWidth="1"/>
+    <col min="8" max="16384" width="8.33203125" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="29" t="s">
         <v>236</v>
       </c>
     </row>
@@ -6027,11 +6060,11 @@
       <c r="G8" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="111" t="s">
+      <c r="H8" s="44" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="2:8" customFormat="1" ht="58.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" customFormat="1" ht="58.5" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>2</v>
       </c>
@@ -6050,265 +6083,265 @@
       <c r="G9" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="111" t="s">
+      <c r="H9" s="44" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="2:8" customFormat="1" ht="115.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="2">
+    <row r="10" spans="2:8" customFormat="1" ht="115.5" x14ac:dyDescent="0.2">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>744</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="7">
+        <v>45216</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>744</v>
+      </c>
+      <c r="D11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="7">
+        <v>45216</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="124" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>744</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="7">
+        <v>45216</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8">
+        <v>744</v>
+      </c>
+      <c r="D13" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="76">
+        <v>45216</v>
+      </c>
+      <c r="G13" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="125" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
         <v>3</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C14" s="11">
         <v>754</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F14" s="7">
         <v>45531</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="111" t="s">
+      <c r="H14" s="44" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="11" spans="2:8" customFormat="1" ht="87" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
+    <row r="15" spans="2:8" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+      <c r="C15" s="11">
+        <v>754</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="7">
+        <v>45531</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>2</v>
+      </c>
+      <c r="C16" s="11">
+        <v>754</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="7">
+        <v>45531</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="124" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
+      <c r="C17" s="27">
+        <v>754</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="24">
+        <v>45531</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>2</v>
+      </c>
+      <c r="C18" s="78">
+        <v>754</v>
+      </c>
+      <c r="D18" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="114">
+        <v>45531</v>
+      </c>
+      <c r="G18" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="125" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4">
         <v>4</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C19" s="27">
         <v>755</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D19" s="111" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E19" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F19" s="122">
         <v>45580</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G19" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="111" t="s">
+      <c r="H19" s="44" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="2:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="2">
-        <v>5</v>
-      </c>
-      <c r="C12" s="11">
-        <v>758</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="7">
-        <v>45769</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="2">
-        <v>6</v>
-      </c>
-      <c r="C13" s="11">
-        <v>761</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="7">
-        <v>45931</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" customFormat="1" ht="141" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
-        <v>7</v>
-      </c>
-      <c r="C14" s="21">
-        <v>762</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" s="23">
-        <v>45938</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>763</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" customFormat="1" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="2">
-        <v>9</v>
-      </c>
-      <c r="C16" s="11">
-        <v>764</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="7">
-        <v>45972</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H16" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="2">
-        <v>10</v>
-      </c>
-      <c r="C17" s="24">
-        <v>765</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="26">
-        <v>46034</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H17" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="2">
-        <v>11</v>
-      </c>
-      <c r="C18" s="27">
-        <v>766</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H18" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="4">
-        <v>12</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="31">
-        <v>46050</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H19" s="111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="2">
-        <v>13</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="32">
-        <v>46050</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="111" t="s">
-        <v>220</v>
+    <row r="20" spans="1:8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>3</v>
+      </c>
+      <c r="C20" s="11">
+        <v>755</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="120">
+        <v>45580</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="5">
         <v>1</v>
       </c>
@@ -6321,7 +6354,7 @@
       <c r="E21" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="30">
         <v>46065</v>
       </c>
       <c r="G21" s="2"/>
@@ -6329,8 +6362,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:8" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="33"/>
+    <row r="22" spans="1:8" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="29"/>
       <c r="B22" s="11">
         <v>1</v>
       </c>
@@ -6343,38 +6376,38 @@
       <c r="E22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="31" t="s">
         <v>160</v>
       </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="111" t="s">
+      <c r="H22" s="44" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8" customFormat="1" ht="185.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="11">
         <v>2</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <v>762</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="32" t="s">
         <v>161</v>
       </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="111" t="s">
+      <c r="H23" s="44" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:8" customFormat="1" ht="128.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="33"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="11">
         <v>3</v>
       </c>
@@ -6391,12 +6424,12 @@
         <v>162</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="111" t="s">
+      <c r="H24" s="44" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="33"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="11">
         <v>1</v>
       </c>
@@ -6409,16 +6442,16 @@
       <c r="E25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="111" t="s">
+      <c r="G25" s="35"/>
+      <c r="H25" s="44" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="33"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="11">
         <v>2</v>
       </c>
@@ -6431,95 +6464,95 @@
       <c r="E26" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>164</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="111" t="s">
+      <c r="H26" s="44" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:8" customFormat="1" ht="58.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="33"/>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5">
-        <v>744</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>128</v>
+    <row r="27" spans="1:8" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="29"/>
+      <c r="B27" s="11">
+        <v>3</v>
+      </c>
+      <c r="C27" s="11">
+        <v>755</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F27" s="7">
-        <v>45216</v>
+        <v>45580</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" customFormat="1" ht="115.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="5">
-        <v>2</v>
+        <v>177</v>
+      </c>
+      <c r="H27" s="124" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="29"/>
+      <c r="B28" s="11">
+        <v>3</v>
       </c>
       <c r="C28" s="11">
-        <v>754</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>131</v>
+        <v>755</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F28" s="7">
-        <v>45531</v>
+        <v>45580</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H28" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="5">
-        <v>3</v>
+        <v>177</v>
+      </c>
+      <c r="H28" s="124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="29"/>
+      <c r="B29" s="2">
+        <v>5</v>
       </c>
       <c r="C29" s="11">
-        <v>755</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>165</v>
+        <v>758</v>
+      </c>
+      <c r="D29" s="109" t="s">
+        <v>137</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F29" s="7">
-        <v>45580</v>
+        <v>45769</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H29" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
+        <v>139</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A30" s="29"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
       <c r="C30" s="11">
         <v>758</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="18" t="s">
         <v>137</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -6528,135 +6561,135 @@
       <c r="F30" s="7">
         <v>45769</v>
       </c>
-      <c r="G30" s="41" t="s">
+      <c r="G30" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H30" s="111" t="s">
+      <c r="H30" s="44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:8" customFormat="1" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+    <row r="31" spans="1:8" customFormat="1" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="29"/>
       <c r="B31" s="5">
+        <v>4</v>
+      </c>
+      <c r="C31" s="11">
+        <v>758</v>
+      </c>
+      <c r="D31" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="7">
+        <v>45769</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="124" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" customFormat="1" ht="59.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="29"/>
+      <c r="B32" s="5">
+        <v>4</v>
+      </c>
+      <c r="C32" s="11">
+        <v>758</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="7">
+        <v>45769</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="H32" s="124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="29"/>
+      <c r="B33" s="8">
+        <v>4</v>
+      </c>
+      <c r="C33" s="100">
+        <v>758</v>
+      </c>
+      <c r="D33" s="110" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="83">
+        <v>45769</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="H33" s="125" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A34" s="29"/>
+      <c r="B34" s="2">
+        <v>6</v>
+      </c>
+      <c r="C34" s="27">
+        <v>761</v>
+      </c>
+      <c r="D34" s="111" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="116">
+        <v>45931</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29"/>
+      <c r="B35" s="40">
         <v>5</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C35" s="11">
         <v>761</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D35" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F35" s="7">
         <v>45931</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="H31" s="111" t="s">
+      <c r="H35" s="44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="32" spans="1:8" customFormat="1" ht="59.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="5">
-        <v>6</v>
-      </c>
-      <c r="C32" s="11">
-        <v>764</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F32" s="7">
-        <v>45972</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H32" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33"/>
-      <c r="B33" s="5">
-        <v>7</v>
-      </c>
-      <c r="C33" s="24">
-        <v>765</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" s="26">
-        <v>46034</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H33" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="5">
-        <v>8</v>
-      </c>
-      <c r="C34" s="42">
-        <v>766</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="45">
-        <v>9</v>
-      </c>
-      <c r="C35" s="27">
-        <v>767</v>
-      </c>
-      <c r="D35" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" s="34">
-        <v>46065</v>
-      </c>
-      <c r="G35" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="H35" s="111" t="s">
-        <v>222</v>
-      </c>
-    </row>
     <row r="36" spans="1:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="33"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="5">
         <v>1</v>
       </c>
@@ -6669,16 +6702,16 @@
       <c r="E36" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="30">
         <v>46085</v>
       </c>
-      <c r="G36" s="48"/>
+      <c r="G36" s="42"/>
       <c r="H36" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:8" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="5">
         <v>2</v>
       </c>
@@ -6691,138 +6724,138 @@
       <c r="E37" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="30">
         <v>46107</v>
       </c>
-      <c r="G37" s="48"/>
+      <c r="G37" s="42"/>
       <c r="H37" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="38" spans="1:8" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
+    <row r="38" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="29"/>
       <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="C38" s="5">
-        <v>744</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>128</v>
+        <v>5</v>
+      </c>
+      <c r="C38" s="11">
+        <v>761</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F38" s="7">
-        <v>45216</v>
-      </c>
-      <c r="G38" s="51" t="s">
-        <v>176</v>
+        <v>45931</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="H38" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
+    <row r="39" spans="1:8" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A39" s="29"/>
       <c r="B39" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C39" s="11">
-        <v>754</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>131</v>
+        <v>761</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F39" s="7">
-        <v>45531</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>176</v>
+        <v>45931</v>
+      </c>
+      <c r="G39" s="47" t="s">
+        <v>179</v>
       </c>
       <c r="H39" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="11">
-        <v>3</v>
-      </c>
-      <c r="C40" s="11">
-        <v>755</v>
-      </c>
-      <c r="D40" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" s="7">
-        <v>45580</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H40" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="5">
-        <v>4</v>
-      </c>
-      <c r="C41" s="11">
-        <v>758</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="29"/>
+      <c r="B40" s="8">
+        <v>5</v>
+      </c>
+      <c r="C40" s="78">
+        <v>761</v>
+      </c>
+      <c r="D40" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" s="76">
+        <v>45931</v>
+      </c>
+      <c r="G40" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="H40" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="29"/>
+      <c r="B41" s="2">
+        <v>7</v>
+      </c>
+      <c r="C41" s="19">
+        <v>762</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="7">
-        <v>45769</v>
-      </c>
-      <c r="G41" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="H41" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="5">
-        <v>5</v>
-      </c>
-      <c r="C42" s="11">
-        <v>761</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="21">
+        <v>45938</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="105" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="29"/>
+      <c r="B42" s="2">
+        <v>8</v>
+      </c>
+      <c r="C42" s="5">
+        <v>763</v>
+      </c>
+      <c r="D42" s="106" t="s">
+        <v>146</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="7">
-        <v>45931</v>
+        <v>147</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H42" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" customFormat="1" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="5">
-        <v>6</v>
+        <v>149</v>
+      </c>
+      <c r="H42" s="105" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" customFormat="1" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="29"/>
+      <c r="B43" s="2">
+        <v>9</v>
       </c>
       <c r="C43" s="11">
         <v>764</v>
@@ -6837,132 +6870,132 @@
         <v>45972</v>
       </c>
       <c r="G43" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="105" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A44" s="29"/>
+      <c r="B44" s="5">
+        <v>6</v>
+      </c>
+      <c r="C44" s="27">
+        <v>764</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" s="24">
+        <v>45972</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H44" s="105" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="29"/>
+      <c r="B45" s="5">
+        <v>6</v>
+      </c>
+      <c r="C45" s="27">
+        <v>764</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="116">
+        <v>45972</v>
+      </c>
+      <c r="G45" s="23" t="s">
         <v>180</v>
-      </c>
-      <c r="H43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="5">
-        <v>7</v>
-      </c>
-      <c r="C44" s="24">
-        <v>765</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F44" s="26">
-        <v>46034</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="33"/>
-      <c r="B45" s="5">
-        <v>8</v>
-      </c>
-      <c r="C45" s="42">
-        <v>766</v>
-      </c>
-      <c r="D45" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F45" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="G45" s="25" t="s">
-        <v>182</v>
       </c>
       <c r="H45" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:8" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="33"/>
-      <c r="B46" s="45">
-        <v>9</v>
-      </c>
-      <c r="C46" s="27">
-        <v>767</v>
-      </c>
-      <c r="D46" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" s="34">
-        <v>46065</v>
+    <row r="46" spans="1:8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A46" s="29"/>
+      <c r="B46" s="40">
+        <v>6</v>
+      </c>
+      <c r="C46" s="11">
+        <v>764</v>
+      </c>
+      <c r="D46" s="113" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F46" s="7">
+        <v>45972</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H46" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="45.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="5">
-        <v>1</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="52">
-        <v>46085</v>
-      </c>
-      <c r="G47" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="H47" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="45.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="5">
-        <v>2</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="52">
-        <v>46107</v>
-      </c>
-      <c r="G48" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="H48" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="8">
+        <v>6</v>
+      </c>
+      <c r="C47" s="78">
+        <v>764</v>
+      </c>
+      <c r="D47" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="114">
+        <v>45972</v>
+      </c>
+      <c r="G47" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="2">
+        <v>10</v>
+      </c>
+      <c r="C48" s="5">
+        <v>765</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="120">
+        <v>46034</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="105" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:8" customFormat="1" ht="99.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="33"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="11">
         <v>1</v>
       </c>
@@ -6975,252 +7008,252 @@
       <c r="E49" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="G49" s="37"/>
+      <c r="G49" s="33"/>
       <c r="H49" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="50" spans="1:8" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
+    <row r="50" spans="1:8" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="29"/>
       <c r="B50" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C50" s="5">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F50" s="7">
-        <v>45216</v>
-      </c>
-      <c r="G50" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="H50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="33"/>
+        <v>46034</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H50" s="105" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A51" s="29"/>
       <c r="B51" s="5">
-        <v>2</v>
-      </c>
-      <c r="C51" s="11">
-        <v>754</v>
+        <v>7</v>
+      </c>
+      <c r="C51" s="5">
+        <v>765</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="F51" s="7">
-        <v>45531</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>176</v>
+        <v>46034</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="H51" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="11">
-        <v>3</v>
-      </c>
-      <c r="C52" s="11">
-        <v>755</v>
-      </c>
-      <c r="D52" s="40" t="s">
-        <v>165</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="5">
+        <v>7</v>
+      </c>
+      <c r="C52" s="5">
+        <v>765</v>
+      </c>
+      <c r="D52" s="105" t="s">
+        <v>109</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F52" s="7">
-        <v>45580</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>177</v>
+        <v>46034</v>
+      </c>
+      <c r="G52" s="47" t="s">
+        <v>181</v>
       </c>
       <c r="H52" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="33"/>
-      <c r="B53" s="5">
-        <v>4</v>
-      </c>
-      <c r="C53" s="11">
-        <v>758</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F53" s="7">
-        <v>45769</v>
-      </c>
-      <c r="G53" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="H53" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="33"/>
-      <c r="B54" s="5">
-        <v>5</v>
-      </c>
-      <c r="C54" s="11">
-        <v>761</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>140</v>
+    <row r="53" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="29"/>
+      <c r="B53" s="8">
+        <v>7</v>
+      </c>
+      <c r="C53" s="8">
+        <v>765</v>
+      </c>
+      <c r="D53" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="76">
+        <v>46034</v>
+      </c>
+      <c r="G53" s="75" t="s">
+        <v>204</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="29"/>
+      <c r="B54" s="2">
+        <v>11</v>
+      </c>
+      <c r="C54" s="25">
+        <v>766</v>
+      </c>
+      <c r="D54" s="107" t="s">
+        <v>154</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="7">
-        <v>45931</v>
-      </c>
-      <c r="G54" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="H54" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="33"/>
+        <v>112</v>
+      </c>
+      <c r="F54" s="117" t="s">
+        <v>155</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="105" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" customFormat="1" ht="72" x14ac:dyDescent="0.2">
+      <c r="A55" s="29"/>
       <c r="B55" s="5">
-        <v>6</v>
-      </c>
-      <c r="C55" s="11">
-        <v>764</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="C55" s="25">
+        <v>766</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F55" s="7">
-        <v>45972</v>
+        <v>112</v>
+      </c>
+      <c r="F55" s="117" t="s">
+        <v>155</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H55" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
+        <v>170</v>
+      </c>
+      <c r="H55" s="105" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="29"/>
       <c r="B56" s="5">
-        <v>7</v>
-      </c>
-      <c r="C56" s="24">
-        <v>765</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" s="26">
-        <v>46034</v>
-      </c>
-      <c r="G56" s="53" t="s">
-        <v>181</v>
+        <v>8</v>
+      </c>
+      <c r="C56" s="37">
+        <v>766</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="H56" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" customFormat="1" ht="57.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" customFormat="1" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="29"/>
       <c r="B57" s="5">
         <v>8</v>
       </c>
-      <c r="C57" s="42">
+      <c r="C57" s="37">
         <v>766</v>
       </c>
-      <c r="D57" s="43" t="s">
+      <c r="D57" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="25" t="s">
+      <c r="E57" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="44" t="s">
+      <c r="F57" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="G57" s="25" t="s">
+      <c r="G57" s="23" t="s">
         <v>189</v>
       </c>
       <c r="H57" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:8" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="33"/>
-      <c r="B58" s="45">
+    <row r="58" spans="1:8" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="29"/>
+      <c r="B58" s="99">
+        <v>8</v>
+      </c>
+      <c r="C58" s="84">
+        <v>766</v>
+      </c>
+      <c r="D58" s="108" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="75" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" s="118" t="s">
+        <v>155</v>
+      </c>
+      <c r="G58" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="H58" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A59" s="29"/>
+      <c r="B59" s="5">
         <v>9</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C59" s="25">
         <v>767</v>
       </c>
-      <c r="D58" s="46" t="s">
+      <c r="D59" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="F58" s="34">
+      <c r="F59" s="46">
         <v>46065</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H58" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="33"/>
-      <c r="B59" s="5">
-        <v>1</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F59" s="52">
-        <v>46085</v>
-      </c>
-      <c r="G59" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="H59" t="s">
-        <v>226</v>
+      <c r="G59" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="H59" s="105" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
@@ -7233,14 +7266,14 @@
       <c r="D60" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="104">
+      <c r="F60" s="92">
         <v>46147</v>
       </c>
-      <c r="G60" s="102"/>
-      <c r="H60" s="33" t="s">
+      <c r="G60" s="90"/>
+      <c r="H60" s="29" t="s">
         <v>218</v>
       </c>
     </row>
@@ -7257,11 +7290,11 @@
       <c r="E61" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F61" s="103">
+      <c r="F61" s="91">
         <v>46161</v>
       </c>
-      <c r="G61" s="54"/>
-      <c r="H61" s="33" t="s">
+      <c r="G61" s="48"/>
+      <c r="H61" s="29" t="s">
         <v>218</v>
       </c>
     </row>
@@ -7278,11 +7311,11 @@
       <c r="E62" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="30">
         <v>46167</v>
       </c>
-      <c r="G62" s="54"/>
-      <c r="H62" s="33" t="s">
+      <c r="G62" s="48"/>
+      <c r="H62" s="29" t="s">
         <v>218</v>
       </c>
     </row>
@@ -7299,16 +7332,16 @@
       <c r="E63" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="30">
         <v>46167</v>
       </c>
-      <c r="G63" s="54"/>
-      <c r="H63" s="33" t="s">
+      <c r="G63" s="48"/>
+      <c r="H63" s="29" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="80">
+      <c r="B64" s="74">
         <v>5</v>
       </c>
       <c r="C64" s="11" t="s">
@@ -7320,35 +7353,35 @@
       <c r="E64" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F64" s="34">
+      <c r="F64" s="30">
         <v>46167</v>
       </c>
-      <c r="G64" s="54"/>
-      <c r="H64" s="33" t="s">
+      <c r="G64" s="48"/>
+      <c r="H64" s="29" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="165" hidden="1" x14ac:dyDescent="0.2">
       <c r="B65" s="11"/>
-      <c r="C65" s="84">
+      <c r="C65" s="78">
         <v>755</v>
       </c>
-      <c r="D65" s="85" t="s">
+      <c r="D65" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="81" t="s">
+      <c r="E65" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="F65" s="82">
+      <c r="F65" s="76">
         <v>45580</v>
       </c>
-      <c r="G65" s="50"/>
-      <c r="H65" s="33" t="s">
+      <c r="G65" s="44"/>
+      <c r="H65" s="29" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="86.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="55">
+      <c r="B66" s="49">
         <v>1</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -7360,320 +7393,327 @@
       <c r="E66" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F66" s="49" t="s">
+      <c r="F66" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="G66" s="37"/>
-      <c r="H66" s="33" t="s">
+      <c r="G66" s="33"/>
+      <c r="H66" s="29" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="45" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="8">
+    <row r="67" spans="2:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="B67" s="5">
+        <v>9</v>
+      </c>
+      <c r="C67" s="25">
+        <v>767</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" s="30">
+        <v>46065</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H67" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="5">
+        <v>9</v>
+      </c>
+      <c r="C68" s="25">
+        <v>767</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" s="30">
+        <v>46065</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H68" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B69" s="89">
+        <v>9</v>
+      </c>
+      <c r="C69" s="84">
+        <v>767</v>
+      </c>
+      <c r="D69" s="78" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="86">
+        <v>46065</v>
+      </c>
+      <c r="G69" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="H69" s="29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="5">
         <v>1</v>
       </c>
-      <c r="C67" s="8">
-        <v>744</v>
-      </c>
-      <c r="D67" s="81" t="s">
-        <v>128</v>
-      </c>
-      <c r="E67" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="F67" s="82">
-        <v>45216</v>
-      </c>
-      <c r="G67" s="83" t="s">
-        <v>176</v>
-      </c>
-      <c r="H67" s="33" t="s">
+      <c r="C70" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" s="102" t="s">
+        <v>173</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F70" s="30">
+        <v>46085</v>
+      </c>
+      <c r="G70" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="H70" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="58.5" x14ac:dyDescent="0.2">
+      <c r="B71" s="5">
+        <v>1</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="30">
+        <v>46085</v>
+      </c>
+      <c r="G71" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="H71" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B72" s="8">
+        <v>1</v>
+      </c>
+      <c r="C72" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" s="100" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="F72" s="121">
+        <v>46085</v>
+      </c>
+      <c r="G72" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="H72" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="8">
+    <row r="73" spans="2:8" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="5">
         <v>2</v>
       </c>
-      <c r="C68" s="84">
-        <v>754</v>
-      </c>
-      <c r="D68" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="F68" s="82">
-        <v>45531</v>
-      </c>
-      <c r="G68" s="83" t="s">
-        <v>176</v>
-      </c>
-      <c r="H68" s="33" t="s">
+      <c r="C73" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" s="119">
+        <v>46107</v>
+      </c>
+      <c r="G73" s="123" t="s">
+        <v>185</v>
+      </c>
+      <c r="H73" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B74" s="99">
+        <v>2</v>
+      </c>
+      <c r="C74" s="78" t="s">
+        <v>193</v>
+      </c>
+      <c r="D74" s="85" t="s">
+        <v>194</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="86">
+        <v>46161</v>
+      </c>
+      <c r="G74" s="88" t="s">
+        <v>207</v>
+      </c>
+      <c r="H74" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="72" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="8">
-        <v>4</v>
-      </c>
-      <c r="C69" s="84">
-        <v>758</v>
-      </c>
-      <c r="D69" s="86" t="s">
-        <v>137</v>
-      </c>
-      <c r="E69" s="81" t="s">
-        <v>138</v>
-      </c>
-      <c r="F69" s="82">
-        <v>45769</v>
-      </c>
-      <c r="G69" s="87" t="s">
-        <v>202</v>
-      </c>
-      <c r="H69" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" ht="58.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="8">
-        <v>5</v>
-      </c>
-      <c r="C70" s="84">
-        <v>761</v>
-      </c>
-      <c r="D70" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="E70" s="81" t="s">
-        <v>141</v>
-      </c>
-      <c r="F70" s="82">
-        <v>45931</v>
-      </c>
-      <c r="G70" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="H70" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" ht="58.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="8">
-        <v>6</v>
-      </c>
-      <c r="C71" s="84">
-        <v>764</v>
-      </c>
-      <c r="D71" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="E71" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="F71" s="82">
-        <v>45972</v>
-      </c>
-      <c r="G71" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="H71" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="8">
-        <v>7</v>
-      </c>
-      <c r="C72" s="89">
-        <v>765</v>
-      </c>
-      <c r="D72" s="90" t="s">
-        <v>109</v>
-      </c>
-      <c r="E72" s="90" t="s">
-        <v>110</v>
-      </c>
-      <c r="F72" s="91">
-        <v>46034</v>
-      </c>
-      <c r="G72" s="81" t="s">
-        <v>204</v>
-      </c>
-      <c r="H72" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="133.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="8">
-        <v>8</v>
-      </c>
-      <c r="C73" s="92">
-        <v>766</v>
-      </c>
-      <c r="D73" s="93" t="s">
-        <v>154</v>
-      </c>
-      <c r="E73" s="90" t="s">
-        <v>112</v>
-      </c>
-      <c r="F73" s="94" t="s">
-        <v>155</v>
-      </c>
-      <c r="G73" s="90" t="s">
-        <v>205</v>
-      </c>
-      <c r="H73" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="101">
-        <v>9</v>
-      </c>
-      <c r="C74" s="95">
-        <v>767</v>
-      </c>
-      <c r="D74" s="96" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" s="84" t="s">
-        <v>159</v>
-      </c>
-      <c r="F74" s="97">
-        <v>46065</v>
-      </c>
-      <c r="G74" s="81" t="s">
-        <v>206</v>
-      </c>
-      <c r="H74" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="45.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" ht="45.75" x14ac:dyDescent="0.2">
       <c r="B75" s="8">
-        <v>1</v>
-      </c>
-      <c r="C75" s="84" t="s">
-        <v>172</v>
-      </c>
-      <c r="D75" s="84" t="s">
-        <v>173</v>
+        <v>3</v>
+      </c>
+      <c r="C75" s="78" t="s">
+        <v>195</v>
+      </c>
+      <c r="D75" s="78" t="s">
+        <v>196</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F75" s="98">
-        <v>46085</v>
-      </c>
-      <c r="G75" s="99" t="s">
-        <v>213</v>
-      </c>
-      <c r="H75" s="33" t="s">
+      <c r="F75" s="87">
+        <v>46167</v>
+      </c>
+      <c r="G75" s="88" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="45.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8" ht="45.75" x14ac:dyDescent="0.2">
       <c r="B76" s="8">
-        <v>2</v>
-      </c>
-      <c r="C76" s="84" t="s">
-        <v>193</v>
-      </c>
-      <c r="D76" s="84" t="s">
-        <v>194</v>
+        <v>4</v>
+      </c>
+      <c r="C76" s="78" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" s="78" t="s">
+        <v>198</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F76" s="98">
-        <v>46161</v>
-      </c>
-      <c r="G76" s="99" t="s">
-        <v>207</v>
-      </c>
-      <c r="H76" s="33" t="s">
+      <c r="F76" s="87">
+        <v>46167</v>
+      </c>
+      <c r="G76" s="88" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="45.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="8">
-        <v>3</v>
-      </c>
-      <c r="C77" s="84" t="s">
-        <v>195</v>
-      </c>
-      <c r="D77" s="84" t="s">
-        <v>196</v>
+    <row r="77" spans="2:8" ht="45.75" x14ac:dyDescent="0.2">
+      <c r="B77" s="89">
+        <v>5</v>
+      </c>
+      <c r="C77" s="78" t="s">
+        <v>199</v>
+      </c>
+      <c r="D77" s="78" t="s">
+        <v>200</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F77" s="98">
+      <c r="F77" s="87">
         <v>46167</v>
       </c>
-      <c r="G77" s="99" t="s">
+      <c r="G77" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="H77" s="33" t="s">
+      <c r="H77" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="45.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="8">
-        <v>4</v>
-      </c>
-      <c r="C78" s="84" t="s">
-        <v>197</v>
-      </c>
-      <c r="D78" s="84" t="s">
-        <v>198</v>
-      </c>
-      <c r="E78" s="8" t="s">
+    <row r="78" spans="2:8" ht="45.75" x14ac:dyDescent="0.2">
+      <c r="B78" s="2">
+        <v>12</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F78" s="98">
-        <v>46167</v>
-      </c>
-      <c r="G78" s="99" t="s">
-        <v>208</v>
-      </c>
-      <c r="H78" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="45.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="100">
-        <v>5</v>
-      </c>
-      <c r="C79" s="84" t="s">
-        <v>199</v>
-      </c>
-      <c r="D79" s="84" t="s">
-        <v>200</v>
-      </c>
-      <c r="E79" s="8" t="s">
+      <c r="F78" s="28">
+        <v>46050</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H78" s="105" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="45.75" x14ac:dyDescent="0.2">
+      <c r="B79" s="2">
+        <v>13</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F79" s="98">
-        <v>46167</v>
-      </c>
-      <c r="G79" s="99" t="s">
-        <v>208</v>
-      </c>
-      <c r="H79" s="33" t="s">
-        <v>228</v>
+      <c r="F79" s="28">
+        <v>46050</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H79" s="105" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:H79" xr:uid="{EEA5A48E-A898-47E1-9389-50DCAA2519C9}">
-    <filterColumn colId="1">
+    <filterColumn colId="6">
       <filters>
-        <filter val="733"/>
+        <filter val="p1"/>
+        <filter val="p2"/>
+        <filter val="p3"/>
+        <filter val="p4"/>
+        <filter val="p5"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:H79">
+      <sortCondition ref="C1:C79"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="133" scale="79" fitToHeight="0" orientation="portrait" r:id="rId1"/>
